--- a/excelFile/myexcel.xlsx
+++ b/excelFile/myexcel.xlsx
@@ -4,47 +4,39 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2445" windowWidth="13470" windowHeight="3675"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="mysheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
+  <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t xml:space="preserve">Username </t>
-  </si>
   <si>
     <t>Password</t>
   </si>
   <si>
-    <t>User1</t>
+    <t>Username</t>
   </si>
   <si>
-    <t>Pass1</t>
+    <t>user1</t>
+  </si>
+  <si>
+    <t>pass1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,7 +51,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -67,36 +59,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,48 +366,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
